--- a/src/Referencia_Variaveis/Importancia_Variaveis_Shap_Todas_Notas.xlsx
+++ b/src/Referencia_Variaveis/Importancia_Variaveis_Shap_Todas_Notas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Armazenamento\MBA\TCC\TccMbaUspEsalq\src\Referencia_Variaveis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A1A991-B9EC-4D62-BE1B-8BBDA2B3D25C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E239122-C07C-469F-8F2D-120D09ABB67C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -172,9 +172,6 @@
     <t>Qtde. máq. secar roupa</t>
   </si>
   <si>
-    <t>Dias empregado(a) doméstico(a)</t>
-  </si>
-  <si>
     <t>Qtde. projetores</t>
   </si>
   <si>
@@ -365,6 +362,9 @@
   </si>
   <si>
     <t>Ocupação galpão</t>
+  </si>
+  <si>
+    <t>Qtde. de Dias empregado(a)</t>
   </si>
 </sst>
 </file>
@@ -1708,7 +1708,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>50</v>
+        <v>114</v>
       </c>
       <c r="B43" t="s">
         <v>8</v>
@@ -1731,7 +1731,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B44" t="s">
         <v>15</v>
@@ -1754,7 +1754,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B45" t="s">
         <v>8</v>
@@ -1777,7 +1777,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B46" t="s">
         <v>15</v>
@@ -1800,7 +1800,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B47" t="s">
         <v>8</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B48" t="s">
         <v>8</v>
@@ -1846,7 +1846,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B49" t="s">
         <v>15</v>
@@ -1869,7 +1869,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B50" t="s">
         <v>15</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B51" t="s">
         <v>15</v>
@@ -1915,7 +1915,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B52" t="s">
         <v>15</v>
@@ -1938,7 +1938,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B53" t="s">
         <v>15</v>
@@ -1961,7 +1961,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B54" t="s">
         <v>15</v>
@@ -1984,7 +1984,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B55" t="s">
         <v>15</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B56" t="s">
         <v>15</v>
@@ -2030,7 +2030,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B57" t="s">
         <v>8</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B58" t="s">
         <v>15</v>
@@ -2076,7 +2076,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B59" t="s">
         <v>15</v>
@@ -2099,7 +2099,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B60" t="s">
         <v>15</v>
@@ -2122,7 +2122,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B61" t="s">
         <v>15</v>
@@ -2145,7 +2145,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B62" t="s">
         <v>15</v>
@@ -2168,7 +2168,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B63" t="s">
         <v>15</v>
@@ -2191,7 +2191,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B64" t="s">
         <v>8</v>
@@ -2214,7 +2214,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B65" t="s">
         <v>8</v>
@@ -2237,7 +2237,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B66" t="s">
         <v>15</v>
@@ -2260,7 +2260,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B67" t="s">
         <v>15</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B68" t="s">
         <v>15</v>
@@ -2306,7 +2306,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B69" t="s">
         <v>15</v>
@@ -2329,7 +2329,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B70" t="s">
         <v>15</v>
@@ -2352,7 +2352,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B71" t="s">
         <v>15</v>
@@ -2375,7 +2375,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B72" t="s">
         <v>15</v>
@@ -2398,7 +2398,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B73" t="s">
         <v>15</v>
@@ -2421,7 +2421,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B74" t="s">
         <v>15</v>
@@ -2444,7 +2444,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B75" t="s">
         <v>15</v>
@@ -2467,7 +2467,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B76" t="s">
         <v>15</v>
@@ -2490,7 +2490,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B77" t="s">
         <v>8</v>
@@ -2513,7 +2513,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B78" t="s">
         <v>15</v>
@@ -2536,7 +2536,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B79" t="s">
         <v>15</v>
@@ -2559,7 +2559,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B80" t="s">
         <v>15</v>
@@ -2582,7 +2582,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B81" t="s">
         <v>15</v>
@@ -2605,7 +2605,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B82" t="s">
         <v>15</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B83" t="s">
         <v>15</v>
@@ -2651,7 +2651,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B84" t="s">
         <v>15</v>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B85" t="s">
         <v>15</v>
@@ -2697,7 +2697,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B86" t="s">
         <v>15</v>
@@ -2720,7 +2720,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B87" t="s">
         <v>15</v>
@@ -2743,7 +2743,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B88" t="s">
         <v>15</v>
@@ -2766,7 +2766,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B89" t="s">
         <v>15</v>
@@ -2789,7 +2789,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B90" t="s">
         <v>15</v>
@@ -2812,7 +2812,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B91" t="s">
         <v>15</v>
@@ -2835,7 +2835,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B92" t="s">
         <v>15</v>
@@ -2858,7 +2858,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B93" t="s">
         <v>15</v>
@@ -2881,7 +2881,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B94" t="s">
         <v>15</v>
@@ -2904,7 +2904,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B95" t="s">
         <v>15</v>
@@ -2927,7 +2927,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B96" t="s">
         <v>15</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B97" t="s">
         <v>15</v>
@@ -2973,7 +2973,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B98" t="s">
         <v>15</v>
@@ -2996,7 +2996,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B99" t="s">
         <v>15</v>
@@ -3019,7 +3019,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B100" t="s">
         <v>15</v>
@@ -3042,7 +3042,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B101" t="s">
         <v>15</v>
@@ -3065,7 +3065,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B102" t="s">
         <v>15</v>
@@ -3088,7 +3088,7 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B103" t="s">
         <v>15</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B104" t="s">
         <v>15</v>
@@ -3134,7 +3134,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B105" t="s">
         <v>15</v>
@@ -3157,7 +3157,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B106" t="s">
         <v>15</v>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B107" t="s">
         <v>15</v>
